--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N121_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N121_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.76326332398204</v>
+        <v>6.624030290147083</v>
       </c>
       <c r="D2" t="n">
-        <v>40.78378479943676</v>
+        <v>6.627365029908473</v>
       </c>
       <c r="E2" t="n">
-        <v>9.529027582496866</v>
+        <v>1.548466982155741</v>
       </c>
       <c r="F2" t="n">
-        <v>9.57402934158589</v>
+        <v>1.555779768007707</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.17643762473185</v>
+        <v>6.853671114018925</v>
       </c>
       <c r="D3" t="n">
-        <v>42.24843625802453</v>
+        <v>6.865370891928985</v>
       </c>
       <c r="E3" t="n">
-        <v>9.529027582496866</v>
+        <v>1.548466982155741</v>
       </c>
       <c r="F3" t="n">
-        <v>9.57402934158589</v>
+        <v>1.555779768007707</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.12087394464179</v>
+        <v>4.24464201600429</v>
       </c>
       <c r="D4" t="n">
-        <v>26.09584721503119</v>
+        <v>4.240575172442568</v>
       </c>
       <c r="E4" t="n">
-        <v>9.529027582496866</v>
+        <v>1.548466982155741</v>
       </c>
       <c r="F4" t="n">
-        <v>9.57402934158589</v>
+        <v>1.555779768007707</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.21401344103094</v>
+        <v>3.284777184167528</v>
       </c>
       <c r="D5" t="n">
-        <v>20.35732972938856</v>
+        <v>3.308066081025641</v>
       </c>
       <c r="E5" t="n">
-        <v>9.529027582496866</v>
+        <v>1.548466982155741</v>
       </c>
       <c r="F5" t="n">
-        <v>9.57402934158589</v>
+        <v>1.555779768007707</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.8626196351784</v>
+        <v>5.665175690716491</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01258060750553</v>
+        <v>5.689544348719649</v>
       </c>
       <c r="E6" t="n">
-        <v>9.529027582496866</v>
+        <v>1.548466982155741</v>
       </c>
       <c r="F6" t="n">
-        <v>9.57402934158589</v>
+        <v>1.555779768007707</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.86444843108232</v>
+        <v>2.415472870050877</v>
       </c>
       <c r="D7" t="n">
-        <v>14.76387746126152</v>
+        <v>2.399130087454997</v>
       </c>
       <c r="E7" t="n">
-        <v>9.529027582496866</v>
+        <v>1.548466982155741</v>
       </c>
       <c r="F7" t="n">
-        <v>9.57402934158589</v>
+        <v>1.555779768007707</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.65827400508811</v>
+        <v>4.656969525826818</v>
       </c>
       <c r="D8" t="n">
-        <v>28.56614444045396</v>
+        <v>4.641998471573769</v>
       </c>
       <c r="E8" t="n">
-        <v>9.529027582496866</v>
+        <v>1.548466982155741</v>
       </c>
       <c r="F8" t="n">
-        <v>9.57402934158589</v>
+        <v>1.555779768007707</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>44.20455683247523</v>
+        <v>7.183240485277224</v>
       </c>
       <c r="D9" t="n">
-        <v>44.34489112069389</v>
+        <v>7.206044807112757</v>
       </c>
       <c r="E9" t="n">
-        <v>9.529027582496866</v>
+        <v>1.548466982155741</v>
       </c>
       <c r="F9" t="n">
-        <v>9.57402934158589</v>
+        <v>1.555779768007707</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>33.492943428342</v>
+        <v>5.442603307105576</v>
       </c>
       <c r="D10" t="n">
-        <v>33.60164424963067</v>
+        <v>5.460267190564983</v>
       </c>
       <c r="E10" t="n">
-        <v>9.529027582496866</v>
+        <v>1.548466982155741</v>
       </c>
       <c r="F10" t="n">
-        <v>9.57402934158589</v>
+        <v>1.555779768007707</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
